--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487861_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487861_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.9938</v>
+        <v>5.6139</v>
       </c>
       <c r="E2" t="n">
-        <v>5.0623</v>
+        <v>5.7705</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.06850000000000001</v>
+        <v>-0.1565</v>
       </c>
       <c r="G2" t="n">
         <v>3.0245</v>
@@ -610,13 +610,13 @@
         <v>0.8325</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.0306</v>
+        <v>0.5895</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.5872000000000001</v>
+        <v>0.121</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5565</v>
+        <v>0.4685</v>
       </c>
       <c r="V2" t="n">
         <v>1.1675</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>R. HAYES</t>
+          <t>S. ROMERO SANCHEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.6096</v>
+        <v>4.4245</v>
       </c>
       <c r="E3" t="n">
-        <v>3.391</v>
+        <v>4.3842</v>
       </c>
       <c r="F3" t="n">
-        <v>1.2186</v>
+        <v>0.0403</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8547</v>
+        <v>3.8221</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7885</v>
+        <v>0.3711</v>
       </c>
       <c r="I3" t="n">
-        <v>0.06610000000000001</v>
+        <v>3.451</v>
       </c>
       <c r="J3" t="n">
-        <v>1.6958</v>
+        <v>4.459</v>
       </c>
       <c r="K3" t="n">
-        <v>1.4215</v>
+        <v>0.9018</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2743</v>
+        <v>3.5571</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.8411</v>
+        <v>-0.6369</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.6329</v>
+        <v>-0.5308</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.2082</v>
+        <v>-0.1061</v>
       </c>
       <c r="P3" t="n">
-        <v>0.8325</v>
+        <v>-0.4162</v>
       </c>
       <c r="Q3" t="n">
         <v>-1.0406</v>
       </c>
       <c r="R3" t="n">
-        <v>1.8731</v>
+        <v>0.6244</v>
       </c>
       <c r="S3" t="n">
-        <v>1.755</v>
+        <v>1.0187</v>
       </c>
       <c r="T3" t="n">
-        <v>1.5683</v>
+        <v>0.9659</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1866</v>
+        <v>0.0529</v>
       </c>
       <c r="V3" t="n">
-        <v>1.1675</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.1675</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S. ROMERO SANCHEZ</t>
+          <t>R. HAYES</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.4562</v>
+        <v>3.9248</v>
       </c>
       <c r="E4" t="n">
-        <v>4.5333</v>
+        <v>2.7062</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.0771</v>
+        <v>1.2186</v>
       </c>
       <c r="G4" t="n">
-        <v>3.8221</v>
+        <v>0.8547</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3711</v>
+        <v>0.7885</v>
       </c>
       <c r="I4" t="n">
-        <v>3.451</v>
+        <v>0.06610000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>4.459</v>
+        <v>1.6958</v>
       </c>
       <c r="K4" t="n">
-        <v>0.9018</v>
+        <v>1.4215</v>
       </c>
       <c r="L4" t="n">
-        <v>3.5571</v>
+        <v>0.2743</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.6369</v>
+        <v>-0.8411</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.5308</v>
+        <v>-0.6329</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.1061</v>
+        <v>-0.2082</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.4162</v>
+        <v>0.8325</v>
       </c>
       <c r="Q4" t="n">
         <v>-1.0406</v>
       </c>
       <c r="R4" t="n">
-        <v>0.6244</v>
+        <v>1.8731</v>
       </c>
       <c r="S4" t="n">
-        <v>1.0503</v>
+        <v>1.0701</v>
       </c>
       <c r="T4" t="n">
-        <v>1.1149</v>
+        <v>0.8835</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0646</v>
+        <v>0.1866</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.1675</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.1675</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.4971</v>
+        <v>3.0409</v>
       </c>
       <c r="E5" t="n">
-        <v>2.0332</v>
+        <v>2.3127</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4639</v>
+        <v>0.7282</v>
       </c>
       <c r="G5" t="n">
         <v>-1.1441</v>
@@ -844,13 +844,13 @@
         <v>1.4568</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0477</v>
+        <v>0.4961</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1396</v>
+        <v>0.4191</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1872</v>
+        <v>0.077</v>
       </c>
       <c r="V5" t="n">
         <v>3.2726</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1282</v>
+        <v>1.5978</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4356</v>
+        <v>1.3161</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6927</v>
+        <v>0.2816</v>
       </c>
       <c r="G6" t="n">
         <v>1.4985</v>
@@ -922,13 +922,13 @@
         <v>1.8731</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5246</v>
+        <v>0.9941</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.901</v>
+        <v>-0.0204</v>
       </c>
       <c r="U6" t="n">
-        <v>1.4256</v>
+        <v>1.0146</v>
       </c>
       <c r="V6" t="n">
         <v>0.3538</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.1386</v>
+        <v>-0.3064</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.2277</v>
+        <v>0.5457</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.9108000000000001</v>
+        <v>-0.8521</v>
       </c>
       <c r="G7" t="n">
         <v>-1.0007</v>
@@ -1000,13 +1000,13 @@
         <v>1.6649</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0515</v>
+        <v>0.8837</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1338</v>
+        <v>0.6395999999999999</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1853</v>
+        <v>0.244</v>
       </c>
       <c r="V7" t="n">
         <v>-0.8137</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.8944</v>
+        <v>-0.9704</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.6183999999999999</v>
+        <v>-0.0174</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.276</v>
+        <v>-0.953</v>
       </c>
       <c r="G8" t="n">
         <v>-1.3805</v>
@@ -1078,13 +1078,13 @@
         <v>1.6649</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.8905</v>
+        <v>0.0334</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8482</v>
+        <v>-0.2471</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0424</v>
+        <v>0.2806</v>
       </c>
       <c r="V8" t="n">
         <v>-0.2477</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>O. SIMA FATTY</t>
+          <t>A. MORALES ROS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.191</v>
+        <v>-3.0536</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.1044</v>
+        <v>-1.7594</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.0866</v>
+        <v>-1.2942</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.9833</v>
+        <v>-2.6911</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.015</v>
+        <v>-0.8933</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.9683</v>
+        <v>-1.7978</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.3994</v>
+        <v>-0.7559</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.3904</v>
+        <v>-0.0236</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.008999999999999999</v>
+        <v>-0.7323</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.5839</v>
+        <v>-1.9351</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.6247</v>
+        <v>-0.8697</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.9593</v>
+        <v>-1.0654</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.6244</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>-1.0406</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4162</v>
+        <v>1.0406</v>
       </c>
       <c r="S9" t="n">
-        <v>2.5841</v>
+        <v>1.1764</v>
       </c>
       <c r="T9" t="n">
-        <v>2.3355</v>
+        <v>0.5325</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2486</v>
+        <v>0.644</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.1675</v>
+        <v>-1.539</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>-0.4953</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.1675</v>
+        <v>-1.0437</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. MORALES ROS</t>
+          <t>O. SIMA FATTY</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.5332</v>
+        <v>-3.6912</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.5032</v>
+        <v>-1.6046</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.03</v>
+        <v>-2.0866</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.6911</v>
+        <v>-2.9833</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.8933</v>
+        <v>-2.015</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.7978</v>
+        <v>-0.9683</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.7559</v>
+        <v>-1.3994</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.0236</v>
+        <v>-1.3904</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.7323</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.9351</v>
+        <v>-1.5839</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.8697</v>
+        <v>-0.6247</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.0654</v>
+        <v>-0.9593</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>-0.6244</v>
       </c>
       <c r="Q10" t="n">
         <v>-1.0406</v>
       </c>
       <c r="R10" t="n">
-        <v>1.0406</v>
+        <v>0.4162</v>
       </c>
       <c r="S10" t="n">
-        <v>1.6969</v>
+        <v>1.0839</v>
       </c>
       <c r="T10" t="n">
-        <v>0.7887</v>
+        <v>0.8354</v>
       </c>
       <c r="U10" t="n">
-        <v>0.9082</v>
+        <v>0.2486</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.539</v>
+        <v>-1.1675</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.4953</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.0437</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="11">
@@ -1267,22 +1267,22 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>9.927699999999998</v>
+        <v>10.5803</v>
       </c>
       <c r="E11" t="n">
-        <v>13.0017</v>
+        <v>13.654</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.0738</v>
+        <v>-3.0737</v>
       </c>
       <c r="G11" t="n">
-        <v>0.000100000000000211</v>
+        <v>0.0001000000000006551</v>
       </c>
       <c r="H11" t="n">
-        <v>-3.571899999999999</v>
+        <v>-3.5719</v>
       </c>
       <c r="I11" t="n">
-        <v>3.5718</v>
+        <v>3.571800000000001</v>
       </c>
       <c r="J11" t="n">
         <v>13.0847</v>
@@ -1300,7 +1300,7 @@
         <v>-6.5331</v>
       </c>
       <c r="O11" t="n">
-        <v>-6.5517</v>
+        <v>-6.551699999999999</v>
       </c>
       <c r="P11" t="n">
         <v>1.0407</v>
@@ -1312,13 +1312,13 @@
         <v>11.4465</v>
       </c>
       <c r="S11" t="n">
-        <v>6.6936</v>
+        <v>7.3459</v>
       </c>
       <c r="T11" t="n">
-        <v>3.4768</v>
+        <v>4.1295</v>
       </c>
       <c r="U11" t="n">
-        <v>3.2166</v>
+        <v>3.216800000000001</v>
       </c>
       <c r="V11" t="n">
         <v>2.1935</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>2.382</v>
+        <v>3.1693</v>
       </c>
       <c r="E12" t="n">
-        <v>4.4274</v>
+        <v>4.7489</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.0454</v>
+        <v>-1.5796</v>
       </c>
       <c r="G12" t="n">
         <v>3.863</v>
@@ -1390,13 +1390,13 @@
         <v>1.0406</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.0616</v>
+        <v>-1.2743</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.9134</v>
+        <v>-0.5919</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.1482</v>
+        <v>-0.6824</v>
       </c>
       <c r="V12" t="n">
         <v>-0.4599</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.3567</v>
+        <v>2.3249</v>
       </c>
       <c r="E13" t="n">
-        <v>4.2547</v>
+        <v>3.9333</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.898</v>
+        <v>-1.6083</v>
       </c>
       <c r="G13" t="n">
         <v>1.7593</v>
@@ -1468,13 +1468,13 @@
         <v>1.2487</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.7751</v>
+        <v>-0.8069</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1214</v>
+        <v>-0.4429</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.6536999999999999</v>
+        <v>-0.364</v>
       </c>
       <c r="V13" t="n">
         <v>0.1238</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6173</v>
+        <v>1.0817</v>
       </c>
       <c r="E14" t="n">
-        <v>2.1248</v>
+        <v>2.4463</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.5075</v>
+        <v>-1.3646</v>
       </c>
       <c r="G14" t="n">
         <v>3.1301</v>
@@ -1546,13 +1546,13 @@
         <v>0.6244</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.2859</v>
+        <v>-0.8215</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.7177</v>
+        <v>-0.3962</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.5682</v>
+        <v>-0.4253</v>
       </c>
       <c r="V14" t="n">
         <v>0.23</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>K. SCHUTTE</t>
+          <t>S. NDIAYE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.3635</v>
+        <v>-0.6659</v>
       </c>
       <c r="E15" t="n">
-        <v>0.3683</v>
+        <v>-1.944</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.7318</v>
+        <v>1.2781</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.8212</v>
+        <v>-1.3954</v>
       </c>
       <c r="H15" t="n">
-        <v>0.2279</v>
+        <v>-0.7014</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.0491</v>
+        <v>-0.694</v>
       </c>
       <c r="J15" t="n">
-        <v>1.5303</v>
+        <v>-1.8321</v>
       </c>
       <c r="K15" t="n">
-        <v>1.3344</v>
+        <v>-1.3136</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1959</v>
+        <v>-0.5184</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.3515</v>
+        <v>0.4367</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.1064</v>
+        <v>0.6122</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.245</v>
+        <v>-0.1755</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.6244</v>
+        <v>0.6244</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.0812</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.4568</v>
+        <v>0.6244</v>
       </c>
       <c r="S15" t="n">
-        <v>1.312</v>
+        <v>-0.6025</v>
       </c>
       <c r="T15" t="n">
-        <v>0.9192</v>
+        <v>-0.1119</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3928</v>
+        <v>-0.4906</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.23</v>
+        <v>0.7076</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.23</v>
+        <v>0.7076</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S. NDIAYE</t>
+          <t>D. ROLLINS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.6453</v>
+        <v>-1.0232</v>
       </c>
       <c r="E16" t="n">
-        <v>-2.1583</v>
+        <v>-0.9046</v>
       </c>
       <c r="F16" t="n">
-        <v>1.513</v>
+        <v>-0.1186</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.3954</v>
+        <v>-0.5254</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.7014</v>
+        <v>-0.1727</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.694</v>
+        <v>-0.3527</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.8321</v>
+        <v>0.0584</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.3136</v>
+        <v>0.0192</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.5184</v>
+        <v>0.0392</v>
       </c>
       <c r="M16" t="n">
-        <v>0.4367</v>
+        <v>-0.5838</v>
       </c>
       <c r="N16" t="n">
-        <v>0.6122</v>
+        <v>-0.1919</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.1755</v>
+        <v>-0.3919</v>
       </c>
       <c r="P16" t="n">
-        <v>0.6244</v>
+        <v>-0.6244</v>
       </c>
       <c r="Q16" t="n">
+        <v>-1.0406</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.4162</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.1266</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0.0776</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0.0489</v>
+      </c>
+      <c r="V16" t="n">
         <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0.6244</v>
-      </c>
-      <c r="S16" t="n">
-        <v>-0.5819</v>
-      </c>
-      <c r="T16" t="n">
-        <v>-0.3262</v>
-      </c>
-      <c r="U16" t="n">
-        <v>-0.2557</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0.7076</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0.7076</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. ROLLINS</t>
+          <t>K. SCHUTTE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.0525</v>
+        <v>-1.0295</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.9046</v>
+        <v>-0.3818</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.148</v>
+        <v>-0.6477000000000001</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.5254</v>
+        <v>-0.8212</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.1727</v>
+        <v>0.2279</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.3527</v>
+        <v>-1.0491</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0584</v>
+        <v>1.5303</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0192</v>
+        <v>1.3344</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0392</v>
+        <v>0.1959</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.5838</v>
+        <v>-2.3515</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1919</v>
+        <v>-1.1064</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.3919</v>
+        <v>-1.245</v>
       </c>
       <c r="P17" t="n">
         <v>-0.6244</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.0406</v>
+        <v>-2.0812</v>
       </c>
       <c r="R17" t="n">
-        <v>0.4162</v>
+        <v>1.4568</v>
       </c>
       <c r="S17" t="n">
-        <v>0.09719999999999999</v>
+        <v>0.646</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0776</v>
+        <v>0.1691</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0196</v>
+        <v>0.4769</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-0.23</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. SIENCHE GUEMETA</t>
+          <t>A. RODRIGUEZ AGUILAR</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.7027</v>
+        <v>-1.1794</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.9209</v>
+        <v>0.553</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2182</v>
+        <v>-1.7324</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.9041</v>
+        <v>-1.0006</v>
       </c>
       <c r="H18" t="n">
-        <v>0.431</v>
+        <v>-0.6716</v>
       </c>
       <c r="I18" t="n">
-        <v>-3.3351</v>
+        <v>-0.329</v>
       </c>
       <c r="J18" t="n">
-        <v>-2.508</v>
+        <v>1.6857</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1535</v>
+        <v>0.2022</v>
       </c>
       <c r="L18" t="n">
-        <v>-2.6616</v>
+        <v>1.4834</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.3961</v>
+        <v>-2.6863</v>
       </c>
       <c r="N18" t="n">
-        <v>0.2775</v>
+        <v>-0.8738</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.6735</v>
+        <v>-1.8124</v>
       </c>
       <c r="P18" t="n">
-        <v>0.8325</v>
+        <v>0.4162</v>
       </c>
       <c r="Q18" t="n">
+        <v>-1.0406</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.4568</v>
+      </c>
+      <c r="S18" t="n">
+        <v>-1.4087</v>
+      </c>
+      <c r="T18" t="n">
+        <v>-0.9058</v>
+      </c>
+      <c r="U18" t="n">
+        <v>-0.503</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0.8137</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0.8137</v>
+      </c>
+      <c r="X18" t="n">
         <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0.8325</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0.139</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0.1272</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0.0118</v>
-      </c>
-      <c r="V18" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="W18" t="n">
-        <v>0.4599</v>
-      </c>
-      <c r="X18" t="n">
-        <v>-0.23</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. RODRIGUEZ AGUILAR</t>
+          <t>G. OROZCO DOMINGUEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,40 +1891,40 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.8786</v>
+        <v>-1.9837</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2316</v>
+        <v>-1.1305</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.1102</v>
+        <v>-0.8532</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.0006</v>
+        <v>-1.666</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.6716</v>
+        <v>-0.5116000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.329</v>
+        <v>-1.1544</v>
       </c>
       <c r="J19" t="n">
-        <v>1.6857</v>
+        <v>0.1711</v>
       </c>
       <c r="K19" t="n">
-        <v>0.2022</v>
+        <v>-0.3114</v>
       </c>
       <c r="L19" t="n">
-        <v>1.4834</v>
+        <v>0.4825</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.6863</v>
+        <v>-1.8371</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.8738</v>
+        <v>-0.2002</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.8124</v>
+        <v>-1.6369</v>
       </c>
       <c r="P19" t="n">
         <v>0.4162</v>
@@ -1936,28 +1936,28 @@
         <v>1.4568</v>
       </c>
       <c r="S19" t="n">
-        <v>-2.1079</v>
+        <v>-0.504</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.2272</v>
+        <v>-0.491</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.8807</v>
+        <v>-0.013</v>
       </c>
       <c r="V19" t="n">
-        <v>0.8137</v>
+        <v>-0.23</v>
       </c>
       <c r="W19" t="n">
-        <v>0.8137</v>
+        <v>0.23</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.4599</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>G. OROZCO DOMINGUEZ</t>
+          <t>J. SIENCHE GUEMETA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.9925</v>
+        <v>-2.24</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.3448</v>
+        <v>-2.1352</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.6477000000000001</v>
+        <v>-0.1047</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.666</v>
+        <v>-2.9041</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.5116000000000001</v>
+        <v>0.431</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.1544</v>
+        <v>-3.3351</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1711</v>
+        <v>-2.508</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.3114</v>
+        <v>0.1535</v>
       </c>
       <c r="L20" t="n">
-        <v>0.4825</v>
+        <v>-2.6616</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.8371</v>
+        <v>-0.3961</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.2002</v>
+        <v>0.2775</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.6369</v>
+        <v>-0.6735</v>
       </c>
       <c r="P20" t="n">
-        <v>0.4162</v>
+        <v>0.8325</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.4568</v>
+        <v>0.8325</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5128</v>
+        <v>-0.3983</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7053</v>
+        <v>-0.0871</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1925</v>
+        <v>-0.3111</v>
       </c>
       <c r="V20" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0.4599</v>
+      </c>
+      <c r="X20" t="n">
         <v>-0.23</v>
-      </c>
-      <c r="W20" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="X20" t="n">
-        <v>-0.4599</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.1603</v>
+        <v>-3.3937</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.8316</v>
+        <v>-1.153</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.3287</v>
+        <v>-2.2407</v>
       </c>
       <c r="G21" t="n">
         <v>1.7383</v>
@@ -2092,13 +2092,13 @@
         <v>0.6244</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7738</v>
+        <v>-1.0071</v>
       </c>
       <c r="T21" t="n">
-        <v>0.0619</v>
+        <v>-0.2595</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.8357</v>
+        <v>-0.7476</v>
       </c>
       <c r="V21" t="n">
         <v>-1.6275</v>
@@ -2125,10 +2125,10 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.4883</v>
+        <v>-4.274</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.1728</v>
+        <v>-0.9584</v>
       </c>
       <c r="F22" t="n">
         <v>-3.3156</v>
@@ -2170,10 +2170,10 @@
         <v>0.6244</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1429</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3915</v>
+        <v>-0.1771</v>
       </c>
       <c r="U22" t="n">
         <v>0.2486</v>
@@ -2203,22 +2203,22 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-9.927699999999998</v>
+        <v>-9.2135</v>
       </c>
       <c r="E23" t="n">
-        <v>3.073799999999998</v>
+        <v>3.073999999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>-13.0017</v>
+        <v>-12.2873</v>
       </c>
       <c r="G23" t="n">
         <v>0.0001000000000006551</v>
       </c>
       <c r="H23" t="n">
-        <v>3.571899999999999</v>
+        <v>3.5719</v>
       </c>
       <c r="I23" t="n">
-        <v>-3.571800000000001</v>
+        <v>-3.5718</v>
       </c>
       <c r="J23" t="n">
         <v>13.0849</v>
@@ -2233,7 +2233,7 @@
         <v>-13.0847</v>
       </c>
       <c r="N23" t="n">
-        <v>-2.9611</v>
+        <v>-2.961100000000001</v>
       </c>
       <c r="O23" t="n">
         <v>-10.1234</v>
@@ -2248,13 +2248,13 @@
         <v>10.406</v>
       </c>
       <c r="S23" t="n">
-        <v>-6.693700000000001</v>
+        <v>-5.9793</v>
       </c>
       <c r="T23" t="n">
-        <v>-3.2168</v>
+        <v>-3.2167</v>
       </c>
       <c r="U23" t="n">
-        <v>-3.4769</v>
+        <v>-2.7626</v>
       </c>
       <c r="V23" t="n">
         <v>-2.1936</v>
